--- a/PC_2009/AS_032.xlsx
+++ b/PC_2009/AS_032.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -45,8 +45,14 @@
     <font>
       <b val="1"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -59,8 +65,26 @@
         <bgColor rgb="001F497D"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+        <bgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9E1F2"/>
+        <bgColor rgb="00D9E1F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
+        <bgColor rgb="00E2EFDA"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -82,11 +106,53 @@
         <color rgb="00D9D9D9"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D3D3D3"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D3D3D3"/>
+      </right>
+      <top style="medium">
+        <color rgb="001B365D"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D3D3D3"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D3D3D3"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D3D3D3"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D3D3D3"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D3D3D3"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D3D3D3"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D3D3D3"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D3D3D3"/>
+      </top>
+      <bottom style="double">
+        <color rgb="001B365D"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -102,6 +168,21 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="5" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="5" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="5" fillId="5" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -468,7 +549,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V295"/>
+  <dimension ref="A1:V297"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -516,6 +597,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
@@ -21181,85 +21263,246 @@
       </c>
     </row>
     <row r="295">
-      <c r="A295" s="6" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="C295" s="7">
+      <c r="A295" s="8" t="inlineStr">
+        <is>
+          <t>TOTAL EVM VOTES</t>
+        </is>
+      </c>
+      <c r="B295" s="9" t="inlineStr"/>
+      <c r="C295" s="10">
         <f>SUM(C6:C294)</f>
         <v/>
       </c>
-      <c r="D295" s="7">
+      <c r="D295" s="10">
         <f>SUM(D6:D294)</f>
         <v/>
       </c>
-      <c r="E295" s="7">
+      <c r="E295" s="10">
         <f>SUM(E6:E294)</f>
         <v/>
       </c>
-      <c r="F295" s="7">
+      <c r="F295" s="10">
         <f>SUM(F6:F294)</f>
         <v/>
       </c>
-      <c r="G295" s="7">
+      <c r="G295" s="10">
         <f>SUM(G6:G294)</f>
         <v/>
       </c>
-      <c r="H295" s="7">
+      <c r="H295" s="10">
         <f>SUM(H6:H294)</f>
         <v/>
       </c>
-      <c r="I295" s="7">
+      <c r="I295" s="10">
         <f>SUM(I6:I294)</f>
         <v/>
       </c>
-      <c r="J295" s="7">
+      <c r="J295" s="10">
         <f>SUM(J6:J294)</f>
         <v/>
       </c>
-      <c r="K295" s="7">
+      <c r="K295" s="10">
         <f>SUM(K6:K294)</f>
         <v/>
       </c>
-      <c r="L295" s="7">
+      <c r="L295" s="10">
         <f>SUM(L6:L294)</f>
         <v/>
       </c>
-      <c r="M295" s="7">
+      <c r="M295" s="10">
         <f>SUM(M6:M294)</f>
         <v/>
       </c>
-      <c r="N295" s="7">
+      <c r="N295" s="10">
         <f>SUM(N6:N294)</f>
         <v/>
       </c>
-      <c r="O295" s="7">
+      <c r="O295" s="10">
         <f>SUM(O6:O294)</f>
         <v/>
       </c>
-      <c r="P295" s="7">
+      <c r="P295" s="10">
         <f>SUM(P6:P294)</f>
         <v/>
       </c>
-      <c r="Q295" s="7">
+      <c r="Q295" s="10">
         <f>SUM(Q6:Q294)</f>
         <v/>
       </c>
-      <c r="R295" s="7">
+      <c r="R295" s="10">
         <f>SUM(R6:R294)</f>
         <v/>
       </c>
-      <c r="S295" s="7">
+      <c r="S295" s="10">
         <f>SUM(S6:S294)</f>
         <v/>
       </c>
-      <c r="T295" s="7">
+      <c r="T295" s="10">
         <f>SUM(T6:T294)</f>
         <v/>
       </c>
-      <c r="U295" s="7">
+      <c r="U295" s="10">
         <f>SUM(U6:U294)</f>
+        <v/>
+      </c>
+      <c r="V295" s="10">
+        <f>SUM(V6:V294)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" s="11" t="inlineStr">
+        <is>
+          <t>POSTAL BALLOT VOTES</t>
+        </is>
+      </c>
+      <c r="B296" s="12" t="inlineStr"/>
+      <c r="C296" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D296" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E296" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F296" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G296" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H296" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I296" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J296" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K296" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L296" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M296" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N296" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O296" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P296" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q296" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R296" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S296" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T296" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U296" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V296" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" s="14" t="inlineStr">
+        <is>
+          <t>TOTAL VOTES POLLED</t>
+        </is>
+      </c>
+      <c r="B297" s="15" t="inlineStr"/>
+      <c r="C297" s="16">
+        <f>C295+C296</f>
+        <v/>
+      </c>
+      <c r="D297" s="16">
+        <f>D295+D296</f>
+        <v/>
+      </c>
+      <c r="E297" s="16">
+        <f>E295+E296</f>
+        <v/>
+      </c>
+      <c r="F297" s="16">
+        <f>F295+F296</f>
+        <v/>
+      </c>
+      <c r="G297" s="16">
+        <f>G295+G296</f>
+        <v/>
+      </c>
+      <c r="H297" s="16">
+        <f>H295+H296</f>
+        <v/>
+      </c>
+      <c r="I297" s="16">
+        <f>I295+I296</f>
+        <v/>
+      </c>
+      <c r="J297" s="16">
+        <f>J295+J296</f>
+        <v/>
+      </c>
+      <c r="K297" s="16">
+        <f>K295+K296</f>
+        <v/>
+      </c>
+      <c r="L297" s="16">
+        <f>L295+L296</f>
+        <v/>
+      </c>
+      <c r="M297" s="16">
+        <f>M295+M296</f>
+        <v/>
+      </c>
+      <c r="N297" s="16">
+        <f>N295+N296</f>
+        <v/>
+      </c>
+      <c r="O297" s="16">
+        <f>O295+O296</f>
+        <v/>
+      </c>
+      <c r="P297" s="16">
+        <f>P295+P296</f>
+        <v/>
+      </c>
+      <c r="Q297" s="16">
+        <f>Q295+Q296</f>
+        <v/>
+      </c>
+      <c r="R297" s="16">
+        <f>R295+R296</f>
+        <v/>
+      </c>
+      <c r="S297" s="16">
+        <f>S295+S296</f>
+        <v/>
+      </c>
+      <c r="T297" s="16">
+        <f>T295+T296</f>
+        <v/>
+      </c>
+      <c r="U297" s="16">
+        <f>U295+U296</f>
+        <v/>
+      </c>
+      <c r="V297" s="16">
+        <f>V295+V296</f>
         <v/>
       </c>
     </row>
